--- a/knowledge/business_data/DATA001_结构化业务数据_员工花名册.xlsx
+++ b/knowledge/business_data/DATA001_结构化业务数据_员工花名册.xlsx
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="I40" s="26" t="n">
-        <v>45398</v>
+        <v>45032</v>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="I41" s="26" t="n">
-        <v>45794</v>
+        <v>45063</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="I42" s="26" t="n">
-        <v>46191</v>
+        <v>45095</v>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="I46" s="26" t="n">
-        <v>45587</v>
+        <v>45221</v>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="I47" s="26" t="n">
-        <v>45984</v>
+        <v>45253</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="I48" s="26" t="n">
-        <v>46015</v>
+        <v>45284</v>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="I52" s="26" t="n">
-        <v>45386</v>
+        <v>45020</v>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="I53" s="26" t="n">
-        <v>45782</v>
+        <v>45051</v>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="I54" s="26" t="n">
-        <v>46179</v>
+        <v>45083</v>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="I58" s="26" t="n">
-        <v>45575</v>
+        <v>45209</v>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="I59" s="26" t="n">
-        <v>45972</v>
+        <v>45241</v>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="I60" s="26" t="n">
-        <v>46003</v>
+        <v>45272</v>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="I65" s="26" t="n">
-        <v>45794</v>
+        <v>45063</v>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I66" s="26" t="n">
-        <v>46191</v>
+        <v>45095</v>
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="I70" s="26" t="n">
-        <v>45587</v>
+        <v>45221</v>
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="I71" s="26" t="n">
-        <v>45984</v>
+        <v>45619</v>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="I72" s="26" t="n">
-        <v>46015</v>
+        <v>45650</v>
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="I77" s="26" t="n">
-        <v>45782</v>
+        <v>45417</v>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="I78" s="26" t="n">
-        <v>46179</v>
+        <v>45449</v>
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="I83" s="26" t="n">
-        <v>45972</v>
+        <v>45607</v>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="I84" s="26" t="n">
-        <v>46003</v>
+        <v>45638</v>
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="I90" s="26" t="n">
-        <v>46191</v>
+        <v>45826</v>
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="I95" s="26" t="n">
-        <v>45984</v>
+        <v>45619</v>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="I96" s="26" t="n">
-        <v>46015</v>
+        <v>45650</v>
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I114" s="26" t="n">
-        <v>46191</v>
+        <v>45826</v>
       </c>
       <c r="J114" s="7" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="I143" s="26" t="n">
-        <v>45984</v>
+        <v>45619</v>
       </c>
       <c r="J143" s="7" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="I144" s="26" t="n">
-        <v>46015</v>
+        <v>45650</v>
       </c>
       <c r="J144" s="7" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         </is>
       </c>
       <c r="I150" s="26" t="n">
-        <v>46179</v>
+        <v>45814</v>
       </c>
       <c r="J150" s="7" t="inlineStr">
         <is>

--- a/knowledge/business_data/DATA001_结构化业务数据_员工花名册.xlsx
+++ b/knowledge/business_data/DATA001_结构化业务数据_员工花名册.xlsx
@@ -9420,7 +9420,7 @@
         </is>
       </c>
       <c r="I150" s="26" t="n">
-        <v>45814</v>
+        <v>46179</v>
       </c>
       <c r="J150" s="7" t="inlineStr">
         <is>
